--- a/data/trans_dic/P74B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P74B-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su pareja percibe algún tipo de pensión</t>
+          <t>Población que su pareja percibe algún tipo de pensión (tasa de respuesta: 96,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 15,75</t>
+          <t>10,65; 15,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,38; 23,62</t>
+          <t>16,51; 23,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,75; 23,21</t>
+          <t>16,19; 23,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,33; 91,51</t>
+          <t>85,32; 91,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,33; 83,5</t>
+          <t>76,78; 83,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,36; 83,17</t>
+          <t>75,38; 83,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,51; 48,33</t>
+          <t>42,56; 48,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,24; 53,4</t>
+          <t>47,4; 53,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,44; 54,07</t>
+          <t>47,34; 54,11</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,45</t>
+          <t>1,66; 4,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,39</t>
+          <t>5,14; 9,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 11,06</t>
+          <t>6,92; 11,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54,92; 71,08</t>
+          <t>55,04; 71,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,14; 54,4</t>
+          <t>42,19; 54,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,25; 58,86</t>
+          <t>48,29; 58,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,98; 16,1</t>
+          <t>11,12; 16,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,31; 22,61</t>
+          <t>17,16; 22,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,36; 26,55</t>
+          <t>21,16; 26,11</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 11,92</t>
+          <t>3,13; 12,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 20,2</t>
+          <t>6,17; 20,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 20,14</t>
+          <t>8,46; 20,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,03; 95,09</t>
+          <t>61,21; 95,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,27; 72,46</t>
+          <t>41,21; 73,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,62; 62,1</t>
+          <t>33,68; 61,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 21,43</t>
+          <t>10,18; 21,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,38; 33,21</t>
+          <t>17,84; 33,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,16; 30,26</t>
+          <t>17,89; 29,96</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,08</t>
+          <t>6,17; 9,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,75; 14,56</t>
+          <t>10,85; 14,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 14,33</t>
+          <t>10,84; 14,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79,79; 85,74</t>
+          <t>79,66; 85,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,75; 70,87</t>
+          <t>64,87; 71,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,72; 69,29</t>
+          <t>62,7; 69,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,34; 32,26</t>
+          <t>28,29; 32,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,78; 36,74</t>
+          <t>32,78; 36,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,84; 35,81</t>
+          <t>31,84; 36,04</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su pareja percibe algún tipo de pensión</t>
+          <t>Población que su pareja percibe algún tipo de pensión (tasa de respuesta: 96,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64307; 95751</t>
+          <t>64772; 97029</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89943; 129661</t>
+          <t>90658; 129159</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64095; 94440</t>
+          <t>65865; 94521</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>388057; 416172</t>
+          <t>388029; 416052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>425195; 465156</t>
+          <t>427730; 465103</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>334501; 369200</t>
+          <t>334599; 369797</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>451808; 513570</t>
+          <t>452289; 517652</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>522491; 590690</t>
+          <t>524264; 591607</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>403624; 460027</t>
+          <t>402707; 460335</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11229; 29061</t>
+          <t>10871; 29057</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35273; 66869</t>
+          <t>36577; 67093</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55128; 88229</t>
+          <t>55160; 89204</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76106; 98500</t>
+          <t>76270; 98773</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>133844; 172781</t>
+          <t>134004; 171680</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190459; 232344</t>
+          <t>190601; 230846</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86971; 127484</t>
+          <t>88076; 127631</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>178243; 232810</t>
+          <t>176675; 232028</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>254720; 316584</t>
+          <t>252248; 311277</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4326; 18386</t>
+          <t>4826; 19350</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5894; 22917</t>
+          <t>6999; 23201</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12439; 29762</t>
+          <t>12504; 30024</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11426; 17804</t>
+          <t>11461; 17798</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18149; 31866</t>
+          <t>18122; 32167</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18516; 35243</t>
+          <t>19113; 35116</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16368; 37049</t>
+          <t>17598; 37611</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27361; 52281</t>
+          <t>28081; 52858</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35104; 61905</t>
+          <t>36592; 61291</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>87757; 128470</t>
+          <t>87341; 128270</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>147776; 200069</t>
+          <t>149096; 200779</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>144049; 193826</t>
+          <t>146648; 197687</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>488369; 524803</t>
+          <t>487602; 524709</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>594825; 651059</t>
+          <t>595942; 654384</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>561562; 620439</t>
+          <t>561351; 622317</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>574679; 654034</t>
+          <t>573623; 658317</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>751649; 842557</t>
+          <t>751694; 845500</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>715522; 804886</t>
+          <t>715552; 810092</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P74B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P74B-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 15,96</t>
+          <t>10,58; 16,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,51; 23,53</t>
+          <t>16,59; 24,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,19; 23,23</t>
+          <t>15,59; 23,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,32; 91,49</t>
+          <t>85,59; 91,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,78; 83,49</t>
+          <t>76,54; 83,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,38; 83,31</t>
+          <t>75,6; 83,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,56; 48,71</t>
+          <t>42,38; 48,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,4; 53,49</t>
+          <t>47,4; 53,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,34; 54,11</t>
+          <t>47,1; 53,88</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,45</t>
+          <t>1,59; 4,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,42</t>
+          <t>5,29; 9,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 11,18</t>
+          <t>6,77; 10,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,04; 71,27</t>
+          <t>55,03; 71,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,19; 54,05</t>
+          <t>41,46; 53,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,29; 58,48</t>
+          <t>48,31; 58,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,12; 16,12</t>
+          <t>10,96; 15,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,16; 22,54</t>
+          <t>17,37; 22,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,16; 26,11</t>
+          <t>21,23; 26,18</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 12,55</t>
+          <t>2,68; 12,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 20,45</t>
+          <t>5,72; 21,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 20,31</t>
+          <t>8,33; 20,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,21; 95,06</t>
+          <t>61,47; 95,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,21; 73,14</t>
+          <t>42,21; 75,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,68; 61,87</t>
+          <t>33,3; 61,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,18; 21,75</t>
+          <t>9,78; 21,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,84; 33,57</t>
+          <t>17,99; 33,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,89; 29,96</t>
+          <t>17,75; 30,36</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,06</t>
+          <t>6,25; 9,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,85; 14,61</t>
+          <t>10,7; 14,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 14,62</t>
+          <t>10,67; 14,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79,66; 85,73</t>
+          <t>79,55; 85,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,87; 71,23</t>
+          <t>64,96; 71,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,7; 69,5</t>
+          <t>62,9; 69,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,29; 32,47</t>
+          <t>28,27; 32,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,78; 36,87</t>
+          <t>32,67; 36,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,84; 36,04</t>
+          <t>31,84; 36,11</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64772; 97029</t>
+          <t>64323; 97246</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90658; 129159</t>
+          <t>91101; 132383</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65865; 94521</t>
+          <t>63440; 95166</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>388029; 416052</t>
+          <t>389248; 415734</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>427730; 465103</t>
+          <t>426390; 464323</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>334599; 369797</t>
+          <t>335598; 369680</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>452289; 517652</t>
+          <t>450384; 513983</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>524264; 591607</t>
+          <t>524233; 593510</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>402707; 460335</t>
+          <t>400745; 458381</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10871; 29057</t>
+          <t>10361; 29872</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36577; 67093</t>
+          <t>37681; 70450</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55160; 89204</t>
+          <t>54033; 87482</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76270; 98773</t>
+          <t>76268; 98415</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>134004; 171680</t>
+          <t>131674; 171211</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190601; 230846</t>
+          <t>190688; 231314</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88076; 127631</t>
+          <t>86817; 126669</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>176675; 232028</t>
+          <t>178829; 230295</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>252248; 311277</t>
+          <t>253119; 312098</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4826; 19350</t>
+          <t>4130; 18501</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6999; 23201</t>
+          <t>6490; 24737</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12504; 30024</t>
+          <t>12311; 30212</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11461; 17798</t>
+          <t>11510; 17806</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18122; 32167</t>
+          <t>18566; 33131</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19113; 35116</t>
+          <t>18902; 34823</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17598; 37611</t>
+          <t>16908; 37360</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28081; 52858</t>
+          <t>28324; 52670</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36592; 61291</t>
+          <t>36312; 62106</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>87341; 128270</t>
+          <t>88479; 128871</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149096; 200779</t>
+          <t>147053; 202571</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>146648; 197687</t>
+          <t>144249; 193839</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>487602; 524709</t>
+          <t>486902; 525540</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>595942; 654384</t>
+          <t>596811; 652904</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>561351; 622317</t>
+          <t>563172; 622501</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>573623; 658317</t>
+          <t>573265; 654471</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>751694; 845500</t>
+          <t>749077; 841711</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>715552; 810092</t>
+          <t>715717; 811511</t>
         </is>
       </c>
     </row>
